--- a/RPOTN.xlsx
+++ b/RPOTN.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="121">
   <si>
     <t/>
   </si>
@@ -305,6 +305,15 @@
   </si>
   <si>
     <t>32</t>
+  </si>
+  <si>
+    <t>20140801</t>
+  </si>
+  <si>
+    <t>IDM TISU ROL 8'S</t>
+  </si>
+  <si>
+    <t>38</t>
   </si>
   <si>
     <t>20118159</t>
@@ -757,7 +766,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1390,18 +1399,18 @@
         <v>4</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -1410,35 +1419,35 @@
         <v>4</v>
       </c>
       <c r="E33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -1447,18 +1456,18 @@
         <v>4</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -1467,15 +1476,18 @@
         <v>4</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -1484,15 +1496,15 @@
         <v>4</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -1501,15 +1513,15 @@
         <v>4</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -1518,10 +1530,10 @@
         <v>4</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>115</v>
       </c>
@@ -1537,7 +1549,24 @@
       <c r="E40" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F40" s="1" t="s">
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/RPOTN.xlsx
+++ b/RPOTN.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="124">
   <si>
     <t/>
   </si>
@@ -314,6 +314,15 @@
   </si>
   <si>
     <t>38</t>
+  </si>
+  <si>
+    <t>20040315</t>
+  </si>
+  <si>
+    <t>IDM PORSELEN BTL 800</t>
+  </si>
+  <si>
+    <t>39</t>
   </si>
   <si>
     <t>20118159</t>
@@ -766,7 +775,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1419,55 +1428,55 @@
         <v>4</v>
       </c>
       <c r="E33" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F34" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E34" s="1" t="s">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -1476,18 +1485,18 @@
         <v>4</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -1496,15 +1505,18 @@
         <v>4</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -1513,15 +1525,15 @@
         <v>4</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -1530,15 +1542,15 @@
         <v>4</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -1547,10 +1559,10 @@
         <v>4</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>118</v>
       </c>
@@ -1566,7 +1578,24 @@
       <c r="E41" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F41" s="1" t="s">
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/RPOTN.xlsx
+++ b/RPOTN.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="126">
   <si>
     <t/>
   </si>
@@ -383,6 +383,12 @@
   </si>
   <si>
     <t>12</t>
+  </si>
+  <si>
+    <t>20143353</t>
+  </si>
+  <si>
+    <t>LABEL THERMAL40X30MM</t>
   </si>
 </sst>
 </file>
@@ -775,7 +781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1599,6 +1605,23 @@
         <v>5</v>
       </c>
     </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/RPOTN.xlsx
+++ b/RPOTN.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="104">
   <si>
     <t/>
   </si>
   <si>
-    <t>20054877</t>
-  </si>
-  <si>
-    <t>IDM KP 1W KCL WHL</t>
+    <t>20045052</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR MIN330</t>
   </si>
   <si>
     <t>RPOTN</t>
@@ -28,343 +28,277 @@
     <t>1</t>
   </si>
   <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>PT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20077503</t>
+  </si>
+  <si>
+    <t>IDM BALLPOINT 3S HTM</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
     <t>PT</t>
   </si>
   <si>
-    <t>20052299</t>
-  </si>
-  <si>
-    <t>IDM KTG PLSTK 1W KCL</t>
+    <t>20039153</t>
+  </si>
+  <si>
+    <t>IDM CUTTER BESAR PCS</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20039152</t>
+  </si>
+  <si>
+    <t>IDM GUNTING KECIL</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20071871</t>
+  </si>
+  <si>
+    <t>MAX ISI STPL10-1M 2S</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20074312</t>
+  </si>
+  <si>
+    <t>IDM LAKBAN BNG 2X70</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20036265</t>
+  </si>
+  <si>
+    <t>JOYKO GLUE STIK GS15</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20101246</t>
+  </si>
+  <si>
+    <t>IDM SLTP BNG2S 12X25</t>
+  </si>
+  <si>
+    <t>10038450</t>
+  </si>
+  <si>
+    <t>SNOW.WHITEBOARD HITM</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>10000475</t>
+  </si>
+  <si>
+    <t>MAX STAPLER HD-10</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20004027</t>
+  </si>
+  <si>
+    <t>IDM HANDSOAP CML 375</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20044863</t>
+  </si>
+  <si>
+    <t>IDM SABUT STNLSS 2'S</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>20027963</t>
+  </si>
+  <si>
+    <t>IDM PMBERSH KACA 400</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20028779</t>
+  </si>
+  <si>
+    <t>IDM KRBOL WNG650(BR)</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>20073425</t>
+  </si>
+  <si>
+    <t>IDM P.PRNG JRK.N 650</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>20096641</t>
+  </si>
+  <si>
+    <t>IDM FRSHNS ORANGE 50</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20027166</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP220</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>20079794</t>
+  </si>
+  <si>
+    <t>IDM KAMPER TOILET 5S</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20101464</t>
+  </si>
+  <si>
+    <t>HANNOCHS C/D SNC 12W</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>20109069</t>
+  </si>
+  <si>
+    <t>BAGUS LEM TIKUS PCS</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>20140801</t>
+  </si>
+  <si>
+    <t>IDM TISU ROL 8'S</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>20040315</t>
+  </si>
+  <si>
+    <t>IDM PORSELEN BTL 800</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>20118159</t>
+  </si>
+  <si>
+    <t>KNTONG PL SMPH 50X70</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20054876</t>
-  </si>
-  <si>
-    <t>IDM KP 1W SDG WHL</t>
+    <t>20118160</t>
+  </si>
+  <si>
+    <t>KNTNG PL SMPH 90X120</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20052298</t>
-  </si>
-  <si>
-    <t>IDM KTG PLSTK 1W SDG</t>
+    <t>20118166</t>
+  </si>
+  <si>
+    <t>EPSON RBN/CRTD LX310</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20054875</t>
-  </si>
-  <si>
-    <t>IDM KP 1W BSR WHL</t>
+    <t>20118167</t>
+  </si>
+  <si>
+    <t>PITA.PRTR RFIL LX310</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20052297</t>
-  </si>
-  <si>
-    <t>IDM KTG PLSTK 1W BSR</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20055907</t>
-  </si>
-  <si>
-    <t>PLASTIK PP BESAR</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20055906</t>
-  </si>
-  <si>
-    <t>PLASTIK PP BESAR PLS</t>
+    <t>20136505</t>
+  </si>
+  <si>
+    <t>PRICE/T PROM DOT BSR</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>20055909</t>
-  </si>
-  <si>
-    <t>PLASTIK PP KECIL</t>
+    <t>20136506</t>
+  </si>
+  <si>
+    <t>PRICE/T REG DOT BSR</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>20055908</t>
-  </si>
-  <si>
-    <t>PLASTIK PP SEDANG</t>
+    <t>20136507</t>
+  </si>
+  <si>
+    <t>PRICE PTAG PRM DOT K</t>
   </si>
   <si>
     <t>10</t>
-  </si>
-  <si>
-    <t>20045052</t>
-  </si>
-  <si>
-    <t>INDOMARET AIR MIN330</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>PT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20077503</t>
-  </si>
-  <si>
-    <t>IDM BALLPOINT 3S HTM</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20039153</t>
-  </si>
-  <si>
-    <t>IDM CUTTER BESAR PCS</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20039152</t>
-  </si>
-  <si>
-    <t>IDM GUNTING KECIL</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20071871</t>
-  </si>
-  <si>
-    <t>MAX ISI STPL10-1M 2S</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20074312</t>
-  </si>
-  <si>
-    <t>IDM LAKBAN BNG 2X70</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20036265</t>
-  </si>
-  <si>
-    <t>JOYKO GLUE STIK GS15</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20101246</t>
-  </si>
-  <si>
-    <t>IDM SLTP BNG2S 12X25</t>
-  </si>
-  <si>
-    <t>10038450</t>
-  </si>
-  <si>
-    <t>SNOW.WHITEBOARD HITM</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>10000475</t>
-  </si>
-  <si>
-    <t>MAX STAPLER HD-10</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20004027</t>
-  </si>
-  <si>
-    <t>IDM HANDSOAP CML 375</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20044863</t>
-  </si>
-  <si>
-    <t>IDM SABUT STNLSS 2'S</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>20027963</t>
-  </si>
-  <si>
-    <t>IDM PMBERSH KACA 400</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20028779</t>
-  </si>
-  <si>
-    <t>IDM KRBOL WNG650(BR)</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>20073425</t>
-  </si>
-  <si>
-    <t>IDM P.PRNG JRK.N 650</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>20096641</t>
-  </si>
-  <si>
-    <t>IDM FRSHNS ORANGE 50</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20027166</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP220</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>20079794</t>
-  </si>
-  <si>
-    <t>IDM KAMPER TOILET 5S</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20101464</t>
-  </si>
-  <si>
-    <t>HANNOCHS C/D SNC 12W</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>20109069</t>
-  </si>
-  <si>
-    <t>BAGUS LEM TIKUS PCS</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>20140801</t>
-  </si>
-  <si>
-    <t>IDM TISU ROL 8'S</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>20040315</t>
-  </si>
-  <si>
-    <t>IDM PORSELEN BTL 800</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>20118159</t>
-  </si>
-  <si>
-    <t>KNTONG PL SMPH 50X70</t>
-  </si>
-  <si>
-    <t>20118160</t>
-  </si>
-  <si>
-    <t>KNTNG PL SMPH 90X120</t>
-  </si>
-  <si>
-    <t>20118166</t>
-  </si>
-  <si>
-    <t>EPSON RBN/CRTD LX310</t>
-  </si>
-  <si>
-    <t>20118167</t>
-  </si>
-  <si>
-    <t>PITA.PRTR RFIL LX310</t>
-  </si>
-  <si>
-    <t>20136505</t>
-  </si>
-  <si>
-    <t>PRICE/T PROM DOT BSR</t>
-  </si>
-  <si>
-    <t>20136506</t>
-  </si>
-  <si>
-    <t>PRICE/T REG DOT BSR</t>
-  </si>
-  <si>
-    <t>20136507</t>
-  </si>
-  <si>
-    <t>PRICE PTAG PRM DOT K</t>
   </si>
   <si>
     <t>20136508</t>
@@ -781,7 +715,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -826,18 +760,18 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -846,38 +780,38 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -886,18 +820,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -906,72 +840,78 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -980,15 +920,18 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -997,15 +940,18 @@
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -1014,18 +960,18 @@
         <v>4</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -1034,18 +980,18 @@
         <v>4</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1054,38 +1000,38 @@
         <v>4</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -1094,18 +1040,18 @@
         <v>4</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -1114,18 +1060,18 @@
         <v>4</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1134,18 +1080,18 @@
         <v>4</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1154,18 +1100,18 @@
         <v>4</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>5</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1174,18 +1120,18 @@
         <v>4</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1194,18 +1140,18 @@
         <v>4</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1214,18 +1160,18 @@
         <v>4</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>67</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1234,18 +1180,18 @@
         <v>4</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1254,18 +1200,18 @@
         <v>4</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1274,18 +1220,15 @@
         <v>4</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -1294,18 +1237,18 @@
         <v>4</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>74</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1314,18 +1257,18 @@
         <v>4</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -1334,18 +1277,15 @@
         <v>4</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -1354,18 +1294,15 @@
         <v>4</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -1374,18 +1311,15 @@
         <v>4</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -1394,18 +1328,15 @@
         <v>4</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>9</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -1414,212 +1345,27 @@
         <v>4</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F32" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
